--- a/inputData/Parameters - Copy 5 min.xlsx
+++ b/inputData/Parameters - Copy 5 min.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/asbb/Desktop/Speciale/Master-Thesis-eVTOL/inputData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F35C4828-4593-4C5A-B535-08E924D976C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BDE1C95-1FF3-084D-8A80-E224BFDC5E0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4800" yWindow="2700" windowWidth="14400" windowHeight="8180" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16660" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -647,18 +647,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C49E0-A7B4-734A-8962-DC2A879F4079}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.6640625" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
@@ -669,7 +669,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -680,7 +680,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>46</v>
       </c>
@@ -691,7 +691,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -702,18 +702,18 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>17</v>
       </c>
       <c r="B6" s="4">
-        <v>1.51</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -724,7 +724,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -736,7 +736,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -747,7 +747,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -758,7 +758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>45</v>
       </c>
@@ -769,7 +769,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -780,7 +780,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>42</v>
       </c>
@@ -791,7 +791,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -803,7 +803,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -815,7 +815,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -827,19 +827,19 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>6</v>
       </c>
       <c r="B17" s="4">
-        <f>780/B20</f>
-        <v>156</v>
+        <f>480/B20</f>
+        <v>96</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>41</v>
       </c>
@@ -859,7 +859,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAF0D5EA-53B5-1240-9D84-6FE223856A18}">
   <dimension ref="A1:P59"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="17.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="17.1640625" customWidth="1"/>
@@ -869,7 +869,7 @@
     <col min="8" max="8" width="18.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="9" t="s">
         <v>36</v>
       </c>
@@ -914,7 +914,7 @@
       </c>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -961,7 +961,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1009,7 +1009,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1053,7 +1053,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1</v>
       </c>
@@ -1100,7 +1100,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>1</v>
       </c>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="O6" s="4"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>1</v>
       </c>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="O7" s="4"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1</v>
       </c>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="O8" s="4"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>1</v>
       </c>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O9" s="4"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>1</v>
       </c>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="O10" s="4"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>2</v>
       </c>
@@ -1333,7 +1333,7 @@
         <v>2489</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>2</v>
       </c>
@@ -1371,7 +1371,7 @@
         <v>2090</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>2</v>
       </c>
@@ -1409,7 +1409,7 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>2</v>
       </c>
@@ -1447,7 +1447,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>2</v>
       </c>
@@ -1485,7 +1485,7 @@
         <v>2869</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>2</v>
       </c>
@@ -1523,7 +1523,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>2</v>
       </c>
@@ -1561,7 +1561,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>2</v>
       </c>
@@ -1599,7 +1599,7 @@
         <v>3724</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>3</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>2329</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>3</v>
       </c>
@@ -1675,7 +1675,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>3</v>
       </c>
@@ -1713,7 +1713,7 @@
         <v>2394</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>3</v>
       </c>
@@ -1751,7 +1751,7 @@
         <v>3173</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>3</v>
       </c>
@@ -1789,7 +1789,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>3</v>
       </c>
@@ -1827,7 +1827,7 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>3</v>
       </c>
@@ -1865,7 +1865,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>4</v>
       </c>
@@ -1903,7 +1903,7 @@
         <v>1767</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>4</v>
       </c>
@@ -1941,7 +1941,7 @@
         <v>3059</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>4</v>
       </c>
@@ -1979,7 +1979,7 @@
         <v>1710</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>4</v>
       </c>
@@ -2017,7 +2017,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>4</v>
       </c>
@@ -2055,7 +2055,7 @@
         <v>1729</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>4</v>
       </c>
@@ -2093,7 +2093,7 @@
         <v>2613</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>5</v>
       </c>
@@ -2131,7 +2131,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>5</v>
       </c>
@@ -2169,7 +2169,7 @@
         <v>3287</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>5</v>
       </c>
@@ -2207,7 +2207,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>5</v>
       </c>
@@ -2245,7 +2245,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>5</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>2489</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>6</v>
       </c>
@@ -2321,7 +2321,7 @@
         <v>4408</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>6</v>
       </c>
@@ -2359,7 +2359,7 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>6</v>
       </c>
@@ -2397,7 +2397,7 @@
         <v>1691</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>6</v>
       </c>
@@ -2435,7 +2435,7 @@
         <v>3648</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>7</v>
       </c>
@@ -2473,7 +2473,7 @@
         <v>3040</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>7</v>
       </c>
@@ -2511,7 +2511,7 @@
         <v>2774</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>7</v>
       </c>
@@ -2549,7 +2549,7 @@
         <v>3553</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>8</v>
       </c>
@@ -2587,7 +2587,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>8</v>
       </c>
@@ -2625,7 +2625,7 @@
         <v>3116</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>9</v>
       </c>
@@ -2663,7 +2663,7 @@
         <v>3230</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>1</v>
       </c>
@@ -2697,7 +2697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>2</v>
       </c>
@@ -2731,7 +2731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>3</v>
       </c>
@@ -2765,7 +2765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>4</v>
       </c>
@@ -2799,7 +2799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>5</v>
       </c>
@@ -2833,7 +2833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>6</v>
       </c>
@@ -2865,7 +2865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>7</v>
       </c>
@@ -2897,7 +2897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>8</v>
       </c>
@@ -2929,7 +2929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>9</v>
       </c>
@@ -2961,7 +2961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>10</v>
       </c>
@@ -2993,13 +2993,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G57" s="2"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G58" s="1"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G59" s="1"/>
     </row>
   </sheetData>

--- a/inputData/Parameters - Copy 5 min.xlsx
+++ b/inputData/Parameters - Copy 5 min.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/asbb/Desktop/Speciale/Master-Thesis-eVTOL/inputData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F35C4828-4593-4C5A-B535-08E924D976C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{483800DC-CC0C-5B4C-A08B-24C8D180E202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4800" yWindow="2700" windowWidth="14400" windowHeight="8180" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -647,18 +647,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C49E0-A7B4-734A-8962-DC2A879F4079}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.6640625" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
@@ -669,7 +669,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -680,7 +680,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>46</v>
       </c>
@@ -691,7 +691,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -702,7 +702,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -713,7 +713,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -724,7 +724,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -736,7 +736,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -747,7 +747,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -758,7 +758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>45</v>
       </c>
@@ -769,7 +769,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -780,7 +780,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>42</v>
       </c>
@@ -791,7 +791,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -803,7 +803,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -815,7 +815,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -827,19 +827,19 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>6</v>
       </c>
       <c r="B17" s="4">
-        <f>780/B20</f>
-        <v>156</v>
+        <f>480/B20</f>
+        <v>96</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>41</v>
       </c>
@@ -859,7 +859,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAF0D5EA-53B5-1240-9D84-6FE223856A18}">
   <dimension ref="A1:P59"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="17.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="17.1640625" customWidth="1"/>
@@ -869,7 +869,7 @@
     <col min="8" max="8" width="18.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="9" t="s">
         <v>36</v>
       </c>
@@ -914,7 +914,7 @@
       </c>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -961,7 +961,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1009,7 +1009,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1053,7 +1053,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1</v>
       </c>
@@ -1100,7 +1100,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>1</v>
       </c>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="O6" s="4"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>1</v>
       </c>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="O7" s="4"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1</v>
       </c>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="O8" s="4"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>1</v>
       </c>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O9" s="4"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>1</v>
       </c>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="O10" s="4"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>2</v>
       </c>
@@ -1333,7 +1333,7 @@
         <v>2489</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>2</v>
       </c>
@@ -1371,7 +1371,7 @@
         <v>2090</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>2</v>
       </c>
@@ -1409,7 +1409,7 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>2</v>
       </c>
@@ -1447,7 +1447,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>2</v>
       </c>
@@ -1485,7 +1485,7 @@
         <v>2869</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>2</v>
       </c>
@@ -1523,7 +1523,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>2</v>
       </c>
@@ -1561,7 +1561,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>2</v>
       </c>
@@ -1599,7 +1599,7 @@
         <v>3724</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>3</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>2329</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>3</v>
       </c>
@@ -1675,7 +1675,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>3</v>
       </c>
@@ -1713,7 +1713,7 @@
         <v>2394</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>3</v>
       </c>
@@ -1751,7 +1751,7 @@
         <v>3173</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>3</v>
       </c>
@@ -1789,7 +1789,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>3</v>
       </c>
@@ -1827,7 +1827,7 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>3</v>
       </c>
@@ -1865,7 +1865,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>4</v>
       </c>
@@ -1903,7 +1903,7 @@
         <v>1767</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>4</v>
       </c>
@@ -1941,7 +1941,7 @@
         <v>3059</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>4</v>
       </c>
@@ -1979,7 +1979,7 @@
         <v>1710</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>4</v>
       </c>
@@ -2017,7 +2017,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>4</v>
       </c>
@@ -2055,7 +2055,7 @@
         <v>1729</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>4</v>
       </c>
@@ -2093,7 +2093,7 @@
         <v>2613</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>5</v>
       </c>
@@ -2131,7 +2131,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>5</v>
       </c>
@@ -2169,7 +2169,7 @@
         <v>3287</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>5</v>
       </c>
@@ -2207,7 +2207,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>5</v>
       </c>
@@ -2245,7 +2245,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>5</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>2489</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>6</v>
       </c>
@@ -2321,7 +2321,7 @@
         <v>4408</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>6</v>
       </c>
@@ -2359,7 +2359,7 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>6</v>
       </c>
@@ -2397,7 +2397,7 @@
         <v>1691</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>6</v>
       </c>
@@ -2435,7 +2435,7 @@
         <v>3648</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>7</v>
       </c>
@@ -2473,7 +2473,7 @@
         <v>3040</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>7</v>
       </c>
@@ -2511,7 +2511,7 @@
         <v>2774</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>7</v>
       </c>
@@ -2549,7 +2549,7 @@
         <v>3553</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>8</v>
       </c>
@@ -2587,7 +2587,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>8</v>
       </c>
@@ -2625,7 +2625,7 @@
         <v>3116</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>9</v>
       </c>
@@ -2663,7 +2663,7 @@
         <v>3230</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>1</v>
       </c>
@@ -2697,7 +2697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>2</v>
       </c>
@@ -2731,7 +2731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>3</v>
       </c>
@@ -2765,7 +2765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>4</v>
       </c>
@@ -2799,7 +2799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>5</v>
       </c>
@@ -2833,7 +2833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>6</v>
       </c>
@@ -2865,7 +2865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>7</v>
       </c>
@@ -2897,7 +2897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>8</v>
       </c>
@@ -2929,7 +2929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>9</v>
       </c>
@@ -2961,7 +2961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>10</v>
       </c>
@@ -2993,13 +2993,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G57" s="2"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G58" s="1"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G59" s="1"/>
     </row>
   </sheetData>
